--- a/artfynd/A 39253-2024 artfynd.xlsx
+++ b/artfynd/A 39253-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120495524</v>
+        <v>120495283</v>
       </c>
       <c r="B2" t="n">
-        <v>90580</v>
+        <v>97930</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>548987</v>
+        <v>549045</v>
       </c>
       <c r="R2" t="n">
-        <v>6664931</v>
+        <v>6664945</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120494892</v>
+        <v>120495524</v>
       </c>
       <c r="B3" t="n">
         <v>90580</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>548935</v>
+        <v>548987</v>
       </c>
       <c r="R3" t="n">
-        <v>6665008</v>
+        <v>6664931</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -985,10 +985,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120495199</v>
+        <v>120494892</v>
       </c>
       <c r="B5" t="n">
-        <v>97930</v>
+        <v>90580</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,25 +997,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1025,10 +1025,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>549045</v>
+        <v>548935</v>
       </c>
       <c r="R5" t="n">
-        <v>6664960</v>
+        <v>6665008</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1291,10 +1291,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120495283</v>
+        <v>120495712</v>
       </c>
       <c r="B8" t="n">
-        <v>97930</v>
+        <v>91335</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,25 +1303,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>366</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1331,10 +1331,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>549045</v>
+        <v>549042</v>
       </c>
       <c r="R8" t="n">
-        <v>6664945</v>
+        <v>6664898</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1393,10 +1393,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120495712</v>
+        <v>120495199</v>
       </c>
       <c r="B9" t="n">
-        <v>91335</v>
+        <v>97930</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,25 +1405,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>366</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1433,10 +1433,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>549042</v>
+        <v>549045</v>
       </c>
       <c r="R9" t="n">
-        <v>6664898</v>
+        <v>6664960</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>

--- a/artfynd/A 39253-2024 artfynd.xlsx
+++ b/artfynd/A 39253-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120495283</v>
+        <v>120495524</v>
       </c>
       <c r="B2" t="n">
-        <v>97930</v>
+        <v>90580</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>549045</v>
+        <v>548987</v>
       </c>
       <c r="R2" t="n">
-        <v>6664945</v>
+        <v>6664931</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120495524</v>
+        <v>120495835</v>
       </c>
       <c r="B3" t="n">
-        <v>90580</v>
+        <v>97930</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>548987</v>
+        <v>549086</v>
       </c>
       <c r="R3" t="n">
-        <v>6664931</v>
+        <v>6664954</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120494891</v>
+        <v>120494892</v>
       </c>
       <c r="B4" t="n">
-        <v>91042</v>
+        <v>90580</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,37 +895,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5467</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kådvaxskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phlebia serialis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Donk</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Paddtjärnsflytet, Paddtjärnsflytet, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>548942</v>
+        <v>548935</v>
       </c>
       <c r="R4" t="n">
-        <v>6665013</v>
+        <v>6665008</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -966,7 +963,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -985,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120494892</v>
+        <v>120495199</v>
       </c>
       <c r="B5" t="n">
-        <v>90580</v>
+        <v>97930</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1025,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>548935</v>
+        <v>549045</v>
       </c>
       <c r="R5" t="n">
-        <v>6665008</v>
+        <v>6664960</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1087,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120495835</v>
+        <v>120494891</v>
       </c>
       <c r="B6" t="n">
-        <v>97930</v>
+        <v>91042</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,38 +1095,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>5467</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kådvaxskinn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia serialis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) Donk</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Paddtjärnsflytet, Paddtjärnsflytet, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>549086</v>
+        <v>548942</v>
       </c>
       <c r="R6" t="n">
-        <v>6664954</v>
+        <v>6665013</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1171,6 +1170,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1189,7 +1189,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120495389</v>
+        <v>120495283</v>
       </c>
       <c r="B7" t="n">
         <v>97930</v>
@@ -1229,10 +1229,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>548995</v>
+        <v>549045</v>
       </c>
       <c r="R7" t="n">
-        <v>6664919</v>
+        <v>6664945</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1393,7 +1393,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120495199</v>
+        <v>120495389</v>
       </c>
       <c r="B9" t="n">
         <v>97930</v>
@@ -1433,10 +1433,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>549045</v>
+        <v>548995</v>
       </c>
       <c r="R9" t="n">
-        <v>6664960</v>
+        <v>6664919</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>

--- a/artfynd/A 39253-2024 artfynd.xlsx
+++ b/artfynd/A 39253-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120495199</v>
+        <v>120495712</v>
       </c>
       <c r="B2" t="n">
-        <v>98050</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92699</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>366</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>549045</v>
+        <v>549042</v>
       </c>
       <c r="R2" t="n">
-        <v>6664960</v>
+        <v>6664898</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -777,37 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120495283</v>
+        <v>120494892</v>
       </c>
       <c r="B3" t="n">
-        <v>98050</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>549045</v>
+        <v>548935</v>
       </c>
       <c r="R3" t="n">
-        <v>6664945</v>
+        <v>6665008</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -882,12 +872,7 @@
         <v>120495524</v>
       </c>
       <c r="B4" t="n">
-        <v>90679</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,15 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120495835</v>
+        <v>120495199</v>
       </c>
       <c r="B5" t="n">
-        <v>98050</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1021,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>549086</v>
+        <v>549045</v>
       </c>
       <c r="R5" t="n">
-        <v>6664954</v>
+        <v>6664960</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1083,37 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120495712</v>
+        <v>120495283</v>
       </c>
       <c r="B6" t="n">
-        <v>91435</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>366</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>549042</v>
+        <v>549045</v>
       </c>
       <c r="R6" t="n">
-        <v>6664898</v>
+        <v>6664945</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1185,53 +1160,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120494891</v>
+        <v>120495389</v>
       </c>
       <c r="B7" t="n">
-        <v>91138</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5467</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kådvaxskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phlebia serialis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Donk</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Paddtjärnsflytet, Paddtjärnsflytet, Vstm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>548942</v>
+        <v>548995</v>
       </c>
       <c r="R7" t="n">
-        <v>6665013</v>
+        <v>6664919</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1272,7 +1239,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1291,15 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120495389</v>
+        <v>120495835</v>
       </c>
       <c r="B8" t="n">
-        <v>98050</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1331,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>548995</v>
+        <v>549086</v>
       </c>
       <c r="R8" t="n">
-        <v>6664919</v>
+        <v>6664954</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1390,108 +1351,6 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>120494892</v>
-      </c>
-      <c r="B9" t="n">
-        <v>90679</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Paddtjärnsflytet, Paddtjärnsflytet, Vstm</t>
-        </is>
-      </c>
-      <c r="Q9" t="n">
-        <v>548935</v>
-      </c>
-      <c r="R9" t="n">
-        <v>6665008</v>
-      </c>
-      <c r="S9" t="n">
-        <v>25</v>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>Västmanland</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>Norberg</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>Västmanland</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>Norberg</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>2024-10-19</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>2024-10-19</t>
-        </is>
-      </c>
-      <c r="AD9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT9" t="inlineStr"/>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>Patric Engfeldt</t>
-        </is>
-      </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>Patric Engfeldt</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
